--- a/cicada_ig/SnomedToCdsiObservation.xlsx
+++ b/cicada_ig/SnomedToCdsiObservation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:37:07-05:00</t>
+    <t>2026-09-02T22:18:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cicada_ig/SnomedToCdsiObservation.xlsx
+++ b/cicada_ig/SnomedToCdsiObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="800">
   <si>
     <t>Property</t>
   </si>
@@ -51,10 +51,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T22:18:14-04:00</t>
+    <t>2026-09-06T20:44:07-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Maps SNOMED CT codes to CDSi observation codes used in immunization decision support.</t>
+    <t>Maps SNOMED CT codes to CDSi observation codes used in immunization decision support. Generated from CDC's supporting data.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -90,25 +93,31 @@
     <t>Source</t>
   </si>
   <si>
+    <t>http://fhirfli.dev/fhir/ig/cicada/ValueSet/vaccine-condition-codes-snomed</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>http://fhirfli.dev/fhir/ig/cicada/ValueSet/cdsi-observation-codes-vs</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
     <t>http://snomed.info/sct</t>
   </si>
   <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>https://www.cdc.gov/vaccines/programs/iis/cdsi</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Relationship</t>
+    <t>http://fhirfli.dev/fhir/ig/cicada/CodeSystem/cdsi-observation-codes</t>
   </si>
   <si>
     <t>370388006</t>
   </si>
   <si>
-    <t>Patient immunocompromised</t>
+    <t>Patient Immunocompromised</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -120,10 +129,28 @@
     <t>Immunocompromised</t>
   </si>
   <si>
+    <t>234336002</t>
+  </si>
+  <si>
+    <t>Hemopoietic stem cell transplant [procedure]</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>Recipient of a hematopoietic stem cell transplant</t>
+  </si>
+  <si>
+    <t>23719005</t>
+  </si>
+  <si>
+    <t>Transplantation of bone marrow [procedure]</t>
+  </si>
+  <si>
     <t>50711007</t>
   </si>
   <si>
-    <t>Viral hepatitis type C</t>
+    <t>Viral hepatitis type C [disorder]</t>
   </si>
   <si>
     <t>005</t>
@@ -135,7 +162,7 @@
     <t>77386006</t>
   </si>
   <si>
-    <t>Patient currently pregnant</t>
+    <t>Patient currently pregnant [finding]</t>
   </si>
   <si>
     <t>007</t>
@@ -144,10 +171,70 @@
     <t>Pregnant</t>
   </si>
   <si>
+    <t>102874004</t>
+  </si>
+  <si>
+    <t>Possible pregnancy [finding]</t>
+  </si>
+  <si>
+    <t>255409004</t>
+  </si>
+  <si>
+    <t>Pregnant woman [person]</t>
+  </si>
+  <si>
+    <t>413712001</t>
+  </si>
+  <si>
+    <t>Breastfeeding [mother] [observable entity]</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Breastfeeding</t>
+  </si>
+  <si>
+    <t>230744007</t>
+  </si>
+  <si>
+    <t>Cerebrospinal fluid leak [disorder]</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>Cerebrospinal fluid leaks</t>
+  </si>
+  <si>
+    <t>449840001</t>
+  </si>
+  <si>
+    <t>Cochlear prosthesis in situ [finding]</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>Cochlear implants</t>
+  </si>
+  <si>
+    <t>43252007</t>
+  </si>
+  <si>
+    <t>Cochlear prosthesis, device [physical object]</t>
+  </si>
+  <si>
+    <t>359612003</t>
+  </si>
+  <si>
+    <t>Implantation of cochlear prosthetic device [procedure]</t>
+  </si>
+  <si>
     <t>31323000</t>
   </si>
   <si>
-    <t>Severe combined immunodeficiency disease</t>
+    <t>Severe combined immunodeficiency disease [disorder]</t>
   </si>
   <si>
     <t>013</t>
@@ -159,7 +246,7 @@
     <t>73211009</t>
   </si>
   <si>
-    <t>Diabetes mellitus</t>
+    <t>Diabetes mellitus [disorder]</t>
   </si>
   <si>
     <t>014</t>
@@ -168,10 +255,142 @@
     <t>Diabetes</t>
   </si>
   <si>
+    <t>328383001</t>
+  </si>
+  <si>
+    <t>Chronic liver disease [disorder]</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>Chronic liver disease</t>
+  </si>
+  <si>
+    <t>19943007</t>
+  </si>
+  <si>
+    <t>Cirrhosis of liver [disorder]</t>
+  </si>
+  <si>
+    <t>128238001</t>
+  </si>
+  <si>
+    <t>Chronic heart disease [disorder]</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>Chronic heart disease</t>
+  </si>
+  <si>
+    <t>42343007</t>
+  </si>
+  <si>
+    <t>Congestive heart failure [disorder]</t>
+  </si>
+  <si>
+    <t>57809008</t>
+  </si>
+  <si>
+    <t>Myocardial disease [disorder]</t>
+  </si>
+  <si>
+    <t>12770006</t>
+  </si>
+  <si>
+    <t>Cyanotic congenital heart disease [disorder]</t>
+  </si>
+  <si>
+    <t>53741008</t>
+  </si>
+  <si>
+    <t>Coronary arteriosclerosis [disorder]</t>
+  </si>
+  <si>
+    <t>79619009</t>
+  </si>
+  <si>
+    <t>Mitral valve stenosis [disorder]</t>
+  </si>
+  <si>
+    <t>698247007</t>
+  </si>
+  <si>
+    <t>Cardiac arrhythmia [disorder]</t>
+  </si>
+  <si>
+    <t>413839001</t>
+  </si>
+  <si>
+    <t>Chronic lung disease [disorder]</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>Chronic lung disease</t>
+  </si>
+  <si>
+    <t>13645005</t>
+  </si>
+  <si>
+    <t>Chronic obstructive lung disease [disorder]</t>
+  </si>
+  <si>
+    <t>87433001</t>
+  </si>
+  <si>
+    <t>Pulmonary emphysema [disorder]</t>
+  </si>
+  <si>
+    <t>39871006</t>
+  </si>
+  <si>
+    <t>Chronic respiratory failure [disorder]</t>
+  </si>
+  <si>
+    <t>427896006</t>
+  </si>
+  <si>
+    <t>Chronic respiratory insufficiency [disorder]</t>
+  </si>
+  <si>
+    <t>17097001</t>
+  </si>
+  <si>
+    <t>Chronic disease of respiratory system [disorder]</t>
+  </si>
+  <si>
+    <t>278971009</t>
+  </si>
+  <si>
+    <t>Hepatitis A Immune [Finding]</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>Laboratory Evidence of Immunity or confirmation of Hepatitis A disease</t>
+  </si>
+  <si>
+    <t>271511000</t>
+  </si>
+  <si>
+    <t>Hepatitis B Immune [Finding]</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>Laboratory Evidence of Immunity or confirmation of Hepatitis B disease</t>
+  </si>
+  <si>
     <t>371111005</t>
   </si>
   <si>
-    <t>Measles immune</t>
+    <t>Measles Immune [finding]</t>
   </si>
   <si>
     <t>020</t>
@@ -183,7 +402,7 @@
     <t>371112003</t>
   </si>
   <si>
-    <t>Mumps immune</t>
+    <t>Mumps Immune [finding]</t>
   </si>
   <si>
     <t>021</t>
@@ -195,7 +414,7 @@
     <t>278968001</t>
   </si>
   <si>
-    <t>Rubella immune</t>
+    <t>Rubella Immune [finding]</t>
   </si>
   <si>
     <t>022</t>
@@ -204,34 +423,1996 @@
     <t>Laboratory Evidence of Immunity for Rubella</t>
   </si>
   <si>
+    <t>371113008</t>
+  </si>
+  <si>
+    <t>Varicella Immune</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>Laboratory Evidence of Immunity or confirmation of Varicella disease</t>
+  </si>
+  <si>
+    <t>38907003</t>
+  </si>
+  <si>
+    <t>Varicella [Disorder]</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>Healthcare provider verified history of or diagnosis of Varicella</t>
+  </si>
+  <si>
+    <t>4740000</t>
+  </si>
+  <si>
+    <t>Herpes Zoster [Disorder]</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>Healthcare provider verified history or diagnosis of Herpes Zoster</t>
+  </si>
+  <si>
     <t>86406008</t>
   </si>
   <si>
-    <t>Human immunodeficiency virus infection</t>
+    <t>Human immunodeficiency virus infection [disorder]</t>
   </si>
   <si>
     <t>026</t>
   </si>
   <si>
-    <t>HIV/AIDS - immunocompromised</t>
+    <t>Persons with perinatal HIV infection who do not have evidence of severe immunosuppression and who were vaccinated with MMR before establishment of antiviral therapy [ART]</t>
+  </si>
+  <si>
+    <t>427314002</t>
+  </si>
+  <si>
+    <t>Antiviral therapy [procedure]</t>
+  </si>
+  <si>
+    <t>390798007</t>
+  </si>
+  <si>
+    <t>Asthma finding [finding]</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>Asthma</t>
   </si>
   <si>
     <t>195967001</t>
   </si>
   <si>
-    <t>Asthma</t>
-  </si>
-  <si>
-    <t>027</t>
+    <t>Asthma [disorder]</t>
+  </si>
+  <si>
+    <t>35327006</t>
+  </si>
+  <si>
+    <t>Intussusception [morphologic abnormality]</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>Intussusception</t>
+  </si>
+  <si>
+    <t>49723003</t>
+  </si>
+  <si>
+    <t>Intussusception of intestine [disorder]</t>
+  </si>
+  <si>
+    <t>69776003</t>
+  </si>
+  <si>
+    <t>Acute gastroenteritis [disorder]</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Acute gastroenteritis</t>
   </si>
   <si>
     <t>56717001</t>
   </si>
   <si>
+    <t>Tuberculosis [disorder]</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
     <t>Tuberculosis</t>
   </si>
   <si>
-    <t>031</t>
+    <t>372763006</t>
+  </si>
+  <si>
+    <t>Amantadine [substance]</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>Taken influenza antiviral medications within the previous 48 hours</t>
+  </si>
+  <si>
+    <t>51361008</t>
+  </si>
+  <si>
+    <t>Amantadine [product]</t>
+  </si>
+  <si>
+    <t>372532009</t>
+  </si>
+  <si>
+    <t>Rimantadine [substance]</t>
+  </si>
+  <si>
+    <t>108712009</t>
+  </si>
+  <si>
+    <t>Rimantadine [product]</t>
+  </si>
+  <si>
+    <t>387010007</t>
+  </si>
+  <si>
+    <t>Zanamivir [substance]</t>
+  </si>
+  <si>
+    <t>116100000</t>
+  </si>
+  <si>
+    <t>Zanamivir [product]</t>
+  </si>
+  <si>
+    <t>412261005</t>
+  </si>
+  <si>
+    <t>Oseltamivir [substance]</t>
+  </si>
+  <si>
+    <t>386142008</t>
+  </si>
+  <si>
+    <t>Oseltamivir [product]</t>
+  </si>
+  <si>
+    <t>405742008</t>
+  </si>
+  <si>
+    <t>Aspirin therapy finding [finding]</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>Receiving long-term aspirin therapy</t>
+  </si>
+  <si>
+    <t>76102007</t>
+  </si>
+  <si>
+    <t>Male homosexual [finding]</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>Men who have sex with men</t>
+  </si>
+  <si>
+    <t>225531006</t>
+  </si>
+  <si>
+    <t>Homosexual behavior [finding]</t>
+  </si>
+  <si>
+    <t>225516002</t>
+  </si>
+  <si>
+    <t>Multiple sexual contacts [finding]</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>Not in a long-term, mutually monogamous relationship</t>
+  </si>
+  <si>
+    <t>228460004</t>
+  </si>
+  <si>
+    <t>Multiple current sexual partners [finding]</t>
+  </si>
+  <si>
+    <t>228466005</t>
+  </si>
+  <si>
+    <t>Commitment to sexual relationship [observable entity]</t>
+  </si>
+  <si>
+    <t>225517006</t>
+  </si>
+  <si>
+    <t>Sexual partners [observable entity]</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>Sex partner of Hepatitis B surface antigen-positive persons</t>
+  </si>
+  <si>
+    <t>11723008</t>
+  </si>
+  <si>
+    <t>Contact with [contextual qualifier] [qualifier value]</t>
+  </si>
+  <si>
+    <t>165806002</t>
+  </si>
+  <si>
+    <t>Hepatitis B surface antigen positive [finding]</t>
+  </si>
+  <si>
+    <t>305489005</t>
+  </si>
+  <si>
+    <t>Under care of genitourinary medicine physician [finding]</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>Receives treatment for STD</t>
+  </si>
+  <si>
+    <t>305679000</t>
+  </si>
+  <si>
+    <t>Seen by genitourinary medicine physician [finding]</t>
+  </si>
+  <si>
+    <t>8098009</t>
+  </si>
+  <si>
+    <t>Sexually transmitted infectious disease [disorder]</t>
+  </si>
+  <si>
+    <t>307052004</t>
+  </si>
+  <si>
+    <t>Illicit drug use [finding]</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>Illicit drug use</t>
+  </si>
+  <si>
+    <t>228366006</t>
+  </si>
+  <si>
+    <t>Finding relating to drug misuse behavior [finding]</t>
+  </si>
+  <si>
+    <t>226034001</t>
+  </si>
+  <si>
+    <t>Injecting drug user [finding]</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>Illicit injection drug use</t>
+  </si>
+  <si>
+    <t>228388006</t>
+  </si>
+  <si>
+    <t>Intravenous drug user [finding]</t>
+  </si>
+  <si>
+    <t>145101000119102</t>
+  </si>
+  <si>
+    <t>Intravenous cocaine abuse [disorder]</t>
+  </si>
+  <si>
+    <t>403746009</t>
+  </si>
+  <si>
+    <t>Skin lesion due to intravenous drug abuse [disorder]</t>
+  </si>
+  <si>
+    <t>860699005</t>
+  </si>
+  <si>
+    <t>Deep vein thrombosis of lower extremity due to intravenous drug use [disorder]</t>
+  </si>
+  <si>
+    <t>77176002</t>
+  </si>
+  <si>
+    <t>Smoker [finding]</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>Smoke cigarettes</t>
+  </si>
+  <si>
+    <t>228281002</t>
+  </si>
+  <si>
+    <t>Problem drinker [finding]</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>Alcoholism</t>
+  </si>
+  <si>
+    <t>7200002</t>
+  </si>
+  <si>
+    <t>Alcoholism [disorder]</t>
+  </si>
+  <si>
+    <t>159138004</t>
+  </si>
+  <si>
+    <t>Microbiologist [occupation]</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>Microbiologists routinely exposed to Neisseria meningitidis</t>
+  </si>
+  <si>
+    <t>14698002</t>
+  </si>
+  <si>
+    <t>Medical microbiologist [occupation]</t>
+  </si>
+  <si>
+    <t>24932003</t>
+  </si>
+  <si>
+    <t>Exposure to [contextual qualifier] [qualifier value]</t>
+  </si>
+  <si>
+    <t>17872004</t>
+  </si>
+  <si>
+    <t>Neisseria meningitidis [organism]</t>
+  </si>
+  <si>
+    <t>159282002</t>
+  </si>
+  <si>
+    <t>Laboratory technician [occupation]</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>Microbiology laboratorians who work frequently with S. typhi</t>
+  </si>
+  <si>
+    <t>5595000</t>
+  </si>
+  <si>
+    <t>Salmonella Typhi [organism]</t>
+  </si>
+  <si>
+    <t>26630006</t>
+  </si>
+  <si>
+    <t>Yellow fever virus [organism]</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>Laboratory personnel who might be exposed to YFV</t>
+  </si>
+  <si>
+    <t>59881000</t>
+  </si>
+  <si>
+    <t>Rabies virus [organism]</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>Rabies researchers</t>
+  </si>
+  <si>
+    <t>44172002</t>
+  </si>
+  <si>
+    <t>Human poliovirus [organism]</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>Laboratory workers who handle specimens that might contain polioviruses</t>
+  </si>
+  <si>
+    <t>223366009</t>
+  </si>
+  <si>
+    <t>Healthcare professional [occupation]</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>Health care personnel</t>
+  </si>
+  <si>
+    <t>26369006</t>
+  </si>
+  <si>
+    <t>Public health nurse [occupation]</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>Public safety worker exposed to blood or infection body fluids</t>
+  </si>
+  <si>
+    <t>68867008</t>
+  </si>
+  <si>
+    <t>Public health dentist [occupation]</t>
+  </si>
+  <si>
+    <t>307969004</t>
+  </si>
+  <si>
+    <t>Public health officer [occupation]</t>
+  </si>
+  <si>
+    <t>56466003</t>
+  </si>
+  <si>
+    <t>Public health physician [occupation]</t>
+  </si>
+  <si>
+    <t>56079002</t>
+  </si>
+  <si>
+    <t>Public health veterinarian [occupation]</t>
+  </si>
+  <si>
+    <t>60008001</t>
+  </si>
+  <si>
+    <t>Public health nutritionist [occupation]</t>
+  </si>
+  <si>
+    <t>87612001</t>
+  </si>
+  <si>
+    <t>Blood [substance]</t>
+  </si>
+  <si>
+    <t>32457005</t>
+  </si>
+  <si>
+    <t>Body fluid [substance]</t>
+  </si>
+  <si>
+    <t>158942005</t>
+  </si>
+  <si>
+    <t>Residential child care worker [occupation]</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>Occupational exposure for Hepatitis A</t>
+  </si>
+  <si>
+    <t>158939004</t>
+  </si>
+  <si>
+    <t>Child care officer [occupation]</t>
+  </si>
+  <si>
+    <t>73851001</t>
+  </si>
+  <si>
+    <t>Plumber [general] [occupation]</t>
+  </si>
+  <si>
+    <t>160157004</t>
+  </si>
+  <si>
+    <t>Sewerman [occupation]</t>
+  </si>
+  <si>
+    <t>266006009</t>
+  </si>
+  <si>
+    <t>Food/drink processor [occupation]</t>
+  </si>
+  <si>
+    <t>274272004</t>
+  </si>
+  <si>
+    <t>Catering services occupation [occupation]</t>
+  </si>
+  <si>
+    <t>160133004</t>
+  </si>
+  <si>
+    <t>Packer - food/garden produce [occupation]</t>
+  </si>
+  <si>
+    <t>265940000</t>
+  </si>
+  <si>
+    <t>Animal health occupation [occupation]</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>Veterinarians and their staff</t>
+  </si>
+  <si>
+    <t>159091009</t>
+  </si>
+  <si>
+    <t>Trainer - performing animals [occupation]</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>Animal handlers</t>
+  </si>
+  <si>
+    <t>65853000</t>
+  </si>
+  <si>
+    <t>Student [occupation]</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>Post secondary student</t>
+  </si>
+  <si>
+    <t>257561002</t>
+  </si>
+  <si>
+    <t>Further education establishment [environment]</t>
+  </si>
+  <si>
+    <t>90688005</t>
+  </si>
+  <si>
+    <t>Chronic renal failure syndrome [disorder]</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>Chronic renal failure</t>
+  </si>
+  <si>
+    <t>20078004</t>
+  </si>
+  <si>
+    <t>Substance abuse treatment center [environment]</t>
+  </si>
+  <si>
+    <t>068</t>
+  </si>
+  <si>
+    <t>In drug abuse treatment and prevention facility</t>
+  </si>
+  <si>
+    <t>257656006</t>
+  </si>
+  <si>
+    <t>Penal institution [environment]</t>
+  </si>
+  <si>
+    <t>069</t>
+  </si>
+  <si>
+    <t>In correctional facility</t>
+  </si>
+  <si>
+    <t>410519009</t>
+  </si>
+  <si>
+    <t>At risk context [qualifier value]</t>
+  </si>
+  <si>
+    <t>070</t>
+  </si>
+  <si>
+    <t>Persons at risk during an outbreak</t>
+  </si>
+  <si>
+    <t>443684005</t>
+  </si>
+  <si>
+    <t>Disease outbreak [event]</t>
+  </si>
+  <si>
+    <t>170484009</t>
+  </si>
+  <si>
+    <t>Typhoid carrier [finding]</t>
+  </si>
+  <si>
+    <t>072</t>
+  </si>
+  <si>
+    <t>Intimate exposure to a documented S. typhi carrier</t>
+  </si>
+  <si>
+    <t>12271241000119109</t>
+  </si>
+  <si>
+    <t>Transgender identify [finding]</t>
+  </si>
+  <si>
+    <t>075</t>
+  </si>
+  <si>
+    <t>Transgender person</t>
+  </si>
+  <si>
+    <t>84757009</t>
+  </si>
+  <si>
+    <t>Epilepsy [disorder]</t>
+  </si>
+  <si>
+    <t>076</t>
+  </si>
+  <si>
+    <t>Progressive neurologic disorder</t>
+  </si>
+  <si>
+    <t>192711008</t>
+  </si>
+  <si>
+    <t>Post diphtheria vaccination encephalitis [disorder]</t>
+  </si>
+  <si>
+    <t>079</t>
+  </si>
+  <si>
+    <t>Encephalopathy not attributable to another identifiable cause within 7 days of administration of a previous dose of Tdap, DTP, or DTaP vaccine</t>
+  </si>
+  <si>
+    <t>192710009</t>
+  </si>
+  <si>
+    <t>Post tetanus vaccination encephalitis [disorder]</t>
+  </si>
+  <si>
+    <t>192712001</t>
+  </si>
+  <si>
+    <t>Post pertussis vaccination encephalitis [disorder]</t>
+  </si>
+  <si>
+    <t>293104008</t>
+  </si>
+  <si>
+    <t>Vaccines adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>080</t>
+  </si>
+  <si>
+    <t>Adverse reaction to vaccine component</t>
+  </si>
+  <si>
+    <t>293117006</t>
+  </si>
+  <si>
+    <t>Poliomyelitis vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>081</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Polio</t>
+  </si>
+  <si>
+    <t>451301000124103</t>
+  </si>
+  <si>
+    <t>Adverse reaction caused by Japanese encephalitis virus vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>082</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Japanese Encephalitis</t>
+  </si>
+  <si>
+    <t>429301000124101</t>
+  </si>
+  <si>
+    <t>Adverse reaction to rotavirus vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Rotavirus</t>
+  </si>
+  <si>
+    <t>293122006</t>
+  </si>
+  <si>
+    <t>Typhoid vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>084</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Typhoid</t>
+  </si>
+  <si>
+    <t>420113004</t>
+  </si>
+  <si>
+    <t>Influenza virus vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>085</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Influenza</t>
+  </si>
+  <si>
+    <t>293115003</t>
+  </si>
+  <si>
+    <t>Pertussis vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>086</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Pertussis</t>
+  </si>
+  <si>
+    <t>219085007</t>
+  </si>
+  <si>
+    <t>Adverse reaction to diphtheria vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>087</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Diphtheria</t>
+  </si>
+  <si>
+    <t>219084006</t>
+  </si>
+  <si>
+    <t>Adverse reaction to tetanus vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>088</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Tetanus</t>
+  </si>
+  <si>
+    <t>451331000124106</t>
+  </si>
+  <si>
+    <t>Adverse reaction caused by varicella virus live vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>089</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Varicella</t>
+  </si>
+  <si>
+    <t>429311000124103</t>
+  </si>
+  <si>
+    <t>Adverse reaction to human papillomavirus vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>090</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of HPV</t>
+  </si>
+  <si>
+    <t>219096004</t>
+  </si>
+  <si>
+    <t>Adverse reaction to measles vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>091</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Measles</t>
+  </si>
+  <si>
+    <t>293114004</t>
+  </si>
+  <si>
+    <t>Mumps vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>092</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Mumps</t>
+  </si>
+  <si>
+    <t>293119009</t>
+  </si>
+  <si>
+    <t>Rubella vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>093</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Rubella</t>
+  </si>
+  <si>
+    <t>293116002</t>
+  </si>
+  <si>
+    <t>Pneumococcal vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>094</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Pneumococcal</t>
+  </si>
+  <si>
+    <t>219088009</t>
+  </si>
+  <si>
+    <t>Adverse reaction to meningococcal vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>095</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Meningococcal</t>
+  </si>
+  <si>
+    <t>451111000124103</t>
+  </si>
+  <si>
+    <t>Adverse reaction caused by meningococcal conjugate vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>293126009</t>
+  </si>
+  <si>
+    <t>Hepatitis A vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>096</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Hepatitis A</t>
+  </si>
+  <si>
+    <t>293110008</t>
+  </si>
+  <si>
+    <t>Hepatitis B vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>097</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Hepatitis B</t>
+  </si>
+  <si>
+    <t>293127000</t>
+  </si>
+  <si>
+    <t>Haemophilus influenzae Type B vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>098</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Hib</t>
+  </si>
+  <si>
+    <t>219095000</t>
+  </si>
+  <si>
+    <t>Adverse reaction to yellow fever vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>099</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Yellow Fever</t>
+  </si>
+  <si>
+    <t>451291000124104</t>
+  </si>
+  <si>
+    <t>Adverse reaction caused by zoster vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of live zoster</t>
+  </si>
+  <si>
+    <t>213020009</t>
+  </si>
+  <si>
+    <t>Egg protein allergy [disorder]</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Allergic reaction to egg protein</t>
+  </si>
+  <si>
+    <t>91930004</t>
+  </si>
+  <si>
+    <t>Allergy to eggs [disorder]</t>
+  </si>
+  <si>
+    <t>293309006</t>
+  </si>
+  <si>
+    <t>Gelatin adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to gelatin</t>
+  </si>
+  <si>
+    <t>294847001</t>
+  </si>
+  <si>
+    <t>Gelatin allergy [disorder]</t>
+  </si>
+  <si>
+    <t>300916003</t>
+  </si>
+  <si>
+    <t>Latex allergy [disorder]</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>Allergic reaction to latex</t>
+  </si>
+  <si>
+    <t>441593005</t>
+  </si>
+  <si>
+    <t>Anaphylaxis due to latex [disorder]</t>
+  </si>
+  <si>
+    <t>419522004</t>
+  </si>
+  <si>
+    <t>Gentamycin sensitivity [disorder]</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to gentamicin</t>
+  </si>
+  <si>
+    <t>420094007</t>
+  </si>
+  <si>
+    <t>Gentamicin adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>294469003</t>
+  </si>
+  <si>
+    <t>Gentamicin allergy [disorder]</t>
+  </si>
+  <si>
+    <t>294468006</t>
+  </si>
+  <si>
+    <t>Neomycin allergy [disorder]</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to neomycin</t>
+  </si>
+  <si>
+    <t>292927007</t>
+  </si>
+  <si>
+    <t>Neomycin adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>294466005</t>
+  </si>
+  <si>
+    <t>Streptomycin allergy [disorder]</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to streptomycin</t>
+  </si>
+  <si>
+    <t>292925004</t>
+  </si>
+  <si>
+    <t>Streptomycin adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>294530006</t>
+  </si>
+  <si>
+    <t>Polymyxin B allergy [disorder]</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to polymyxin B</t>
+  </si>
+  <si>
+    <t>292992006</t>
+  </si>
+  <si>
+    <t>Polymyxin B adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>703936006</t>
+  </si>
+  <si>
+    <t>Allergy to yeast [disorder]</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Hypersensitivity to yeast</t>
+  </si>
+  <si>
+    <t>293118001</t>
+  </si>
+  <si>
+    <t>Rabies vaccine adverse reaction [disorder]</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Rabies</t>
+  </si>
+  <si>
+    <t>46177005</t>
+  </si>
+  <si>
+    <t>End stage renal disease [disorder]</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>End stage renal disease</t>
+  </si>
+  <si>
+    <t>443143006</t>
+  </si>
+  <si>
+    <t>Dependence on hemodialysis [finding]</t>
+  </si>
+  <si>
+    <t>714749008</t>
+  </si>
+  <si>
+    <t>Continuous renal replacement therapy [procedure]</t>
+  </si>
+  <si>
+    <t>64520006</t>
+  </si>
+  <si>
+    <t>Protamine sulfate [substance]</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction to protamine sulfate</t>
+  </si>
+  <si>
+    <t>294278007</t>
+  </si>
+  <si>
+    <t>Protamine allergy [disorder]</t>
+  </si>
+  <si>
+    <t>451281000124102</t>
+  </si>
+  <si>
+    <t>Adverse reaction caused by meningococcal group B vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of Meningococcal B</t>
+  </si>
+  <si>
+    <t>219082005</t>
+  </si>
+  <si>
+    <t>Adverse reaction caused by cholera vaccine [disorder]</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Severe allergic reaction after previous dose of cholera</t>
+  </si>
+  <si>
+    <t>32911000</t>
+  </si>
+  <si>
+    <t>Homeless [finding]</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>Homelessness</t>
+  </si>
+  <si>
+    <t>116859006</t>
+  </si>
+  <si>
+    <t>Transfusion of blood product [procedure]</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>RBC [adenine-saline added] blood transfusion</t>
+  </si>
+  <si>
+    <t>13569004</t>
+  </si>
+  <si>
+    <t>Transfusion of plasma [procedure]</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Plasma/platelet products blood transfusion</t>
+  </si>
+  <si>
+    <t>12719002</t>
+  </si>
+  <si>
+    <t>Platelet transfusion [procedure]</t>
+  </si>
+  <si>
+    <t>65880007</t>
+  </si>
+  <si>
+    <t>X-linked agammaglobulinemia [disorder]</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>B-lymphocyte [humoral] - Severe antibody deficiencies</t>
+  </si>
+  <si>
+    <t>23238000</t>
+  </si>
+  <si>
+    <t>Common variable agammaglobulinemia [disorder]</t>
+  </si>
+  <si>
+    <t>190979003</t>
+  </si>
+  <si>
+    <t>Selective immunoglobulin A deficiency [disorder]</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>B-lymphocyte [humoral] - Less severe antibody deficiencies</t>
+  </si>
+  <si>
+    <t>123785006</t>
+  </si>
+  <si>
+    <t>Immunoglobulin G subclass deficiency [finding]</t>
+  </si>
+  <si>
+    <t>77128003</t>
+  </si>
+  <si>
+    <t>DiGeorge sequence [disorder]</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>T-lymphocyte [cell-mediated and humoral] - Complete defects</t>
+  </si>
+  <si>
+    <t>36070007</t>
+  </si>
+  <si>
+    <t>Wiskott-Aldrich syndrome [disorder]</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>T-lymphocyte [cell-mediated and humoral] - Partial defects</t>
+  </si>
+  <si>
+    <t>68504005</t>
+  </si>
+  <si>
+    <t>Ataxia-telangiectasia syndrome [disorder]</t>
+  </si>
+  <si>
+    <t>24743004</t>
+  </si>
+  <si>
+    <t>Complement deficiency disease [disorder]</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>Persistent complement, properdin, or factor B deficiency</t>
+  </si>
+  <si>
+    <t>81166004</t>
+  </si>
+  <si>
+    <t>Properdin deficiency disease [disorder]</t>
+  </si>
+  <si>
+    <t>234605000</t>
+  </si>
+  <si>
+    <t>Factor B deficiency [disorder]</t>
+  </si>
+  <si>
+    <t>387759001</t>
+  </si>
+  <si>
+    <t>Chronic granulomatous disease [disorder]</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>Phagocytic function - Chronic granulomatous disease</t>
+  </si>
+  <si>
+    <t>77358003</t>
+  </si>
+  <si>
+    <t>Congenital leukocyte adherence deficiency [disorder]</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>Phagocytic function - Leukocyte adhesion defect, and myeloperoxidase deficiency</t>
+  </si>
+  <si>
+    <t>234433009</t>
+  </si>
+  <si>
+    <t>Myeloperoxidase deficiency [disorder]</t>
+  </si>
+  <si>
+    <t>62479008</t>
+  </si>
+  <si>
+    <t>Acquired immune deficiency syndrome [disorder]</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>HIV/AIDS - severely immunocompromised</t>
+  </si>
+  <si>
+    <t>313039003</t>
+  </si>
+  <si>
+    <t>Solid organ transplant [procedure]</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Solid organ transplantation</t>
+  </si>
+  <si>
+    <t>86553008</t>
+  </si>
+  <si>
+    <t>Immunosuppressive therapy [procedure]</t>
+  </si>
+  <si>
+    <t>158</t>
+  </si>
+  <si>
+    <t>Immunosuppressive therapy</t>
+  </si>
+  <si>
+    <t>53438000</t>
+  </si>
+  <si>
+    <t>Radiation therapy procedure or service [procedure]</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Radiation therapy</t>
+  </si>
+  <si>
+    <t>707147002</t>
+  </si>
+  <si>
+    <t>Asplenia [disorder]</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Anatomical or functional asplenia</t>
+  </si>
+  <si>
+    <t>709044004</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease [disorder]</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Chronic kidney disease</t>
+  </si>
+  <si>
+    <t>52254009</t>
+  </si>
+  <si>
+    <t>Nephrotic syndrome [disorder]</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Nephrotic Syndrome</t>
+  </si>
+  <si>
+    <t>367336001</t>
+  </si>
+  <si>
+    <t>Chemotherapy [procedure]</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Chemotherapy</t>
+  </si>
+  <si>
+    <t>213017001</t>
+  </si>
+  <si>
+    <t>Sexual abuse [event]</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>History of sexual abuse or assault</t>
+  </si>
+  <si>
+    <t>422608009</t>
+  </si>
+  <si>
+    <t>Sexual assault [finding]</t>
+  </si>
+  <si>
+    <t>248110007</t>
+  </si>
+  <si>
+    <t>Sexual assault [event]</t>
+  </si>
+  <si>
+    <t>248986005</t>
+  </si>
+  <si>
+    <t>Estimated date of conception [observable entity]</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Onset of pregnancy</t>
+  </si>
+  <si>
+    <t>93143009</t>
+  </si>
+  <si>
+    <t>Leukemia, disease [disorder]</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Leukemia</t>
+  </si>
+  <si>
+    <t>399600009</t>
+  </si>
+  <si>
+    <t>Lymphoma [finding]</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Lymphoma</t>
+  </si>
+  <si>
+    <t>118599009</t>
+  </si>
+  <si>
+    <t>Hodgkin's disease [disorder]</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Hodgkin's disease</t>
+  </si>
+  <si>
+    <t>109989006</t>
+  </si>
+  <si>
+    <t>Multiple myeloma [disorder]</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Multiple myeloma</t>
+  </si>
+  <si>
+    <t>1156961008</t>
+  </si>
+  <si>
+    <t>Chimeric antigen receptor T-cell immunotherapy [procedure]</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Receipt of CAR-T-cell therapy</t>
+  </si>
+  <si>
+    <t>363346000</t>
+  </si>
+  <si>
+    <t>Malignant neoplastic disease [disorder]</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Cancer</t>
+  </si>
+  <si>
+    <t>233703007</t>
+  </si>
+  <si>
+    <t>Interstitial lung disease [disorder]</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Interstitial lung disease</t>
+  </si>
+  <si>
+    <t>190905008</t>
+  </si>
+  <si>
+    <t>cystic fibrosis [disorder]</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Cystic fibrosis</t>
+  </si>
+  <si>
+    <t>70995007</t>
+  </si>
+  <si>
+    <t>Pulmonary hypertension [disorder]</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Pulmonary hypertension</t>
+  </si>
+  <si>
+    <t>52448006</t>
+  </si>
+  <si>
+    <t>Dimensia [disorder]</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Dementia</t>
+  </si>
+  <si>
+    <t>41040004</t>
+  </si>
+  <si>
+    <t>Complete trisomy 21 syndrome [disorder]</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>Down syndrome</t>
+  </si>
+  <si>
+    <t>238131007</t>
+  </si>
+  <si>
+    <t>Overweight [finding]</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>Obesity</t>
+  </si>
+  <si>
+    <t>414915002</t>
+  </si>
+  <si>
+    <t>Obese [finding]</t>
+  </si>
+  <si>
+    <t>83911000119104</t>
+  </si>
+  <si>
+    <t>Severe obesity [disorder]</t>
+  </si>
+  <si>
+    <t>40108008</t>
+  </si>
+  <si>
+    <t>Thalassemia [disorder]</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Thalassemia</t>
+  </si>
+  <si>
+    <t>62914000</t>
+  </si>
+  <si>
+    <t>Cerebrovascular disease [disorder]</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>Cerebrovascular disease</t>
+  </si>
+  <si>
+    <t>413490006</t>
+  </si>
+  <si>
+    <t>American Indian or Alaska Native [racial group]</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>American Indian or Alaskan Native</t>
+  </si>
+  <si>
+    <t>370219009</t>
+  </si>
+  <si>
+    <t>Moderate Asthma [disorder]</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Moderate persistent or severe persistent asthma</t>
+  </si>
+  <si>
+    <t>427295004</t>
+  </si>
+  <si>
+    <t>Moderate Persistent Asthma [disorder]</t>
+  </si>
+  <si>
+    <t>370221004</t>
+  </si>
+  <si>
+    <t>Severe Asthma [disorder]</t>
+  </si>
+  <si>
+    <t>426656000</t>
+  </si>
+  <si>
+    <t>Severe Persistent Asthma [disorder]</t>
+  </si>
+  <si>
+    <t>5281000124103</t>
+  </si>
+  <si>
+    <t>Persistent Asthma [disorder]</t>
+  </si>
+  <si>
+    <t>2360001000004109</t>
+  </si>
+  <si>
+    <t>Steroid dependent asthma [disorder]</t>
+  </si>
+  <si>
+    <t>128292002</t>
+  </si>
+  <si>
+    <t>Chronic disease of cardiovascular system [disorder]</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>Chronic cardiovascular disease</t>
+  </si>
+  <si>
+    <t>400047006</t>
+  </si>
+  <si>
+    <t>Peripheral vascular disease [disorder]</t>
+  </si>
+  <si>
+    <t>21631000119105</t>
+  </si>
+  <si>
+    <t>Limb ischemia [disorder]</t>
+  </si>
+  <si>
+    <t>63491006</t>
+  </si>
+  <si>
+    <t>Intermittent claudication [finding]</t>
+  </si>
+  <si>
+    <t>65198009</t>
+  </si>
+  <si>
+    <t>Arterial thrombosis [disorder]</t>
+  </si>
+  <si>
+    <t>111354009</t>
+  </si>
+  <si>
+    <t>Chronic vascular insufficiency of intestine [disorder]</t>
+  </si>
+  <si>
+    <t>59282003</t>
+  </si>
+  <si>
+    <t>Pulmonary embolism [disorder]</t>
+  </si>
+  <si>
+    <t>17920008</t>
+  </si>
+  <si>
+    <t>Portal vein thrombosis [disorder]</t>
+  </si>
+  <si>
+    <t>67362008</t>
+  </si>
+  <si>
+    <t>Aortic aneurysm [disorder]</t>
+  </si>
+  <si>
+    <t>233996000</t>
+  </si>
+  <si>
+    <t>Type II dissection of thoracic aorta [disorder]</t>
+  </si>
+  <si>
+    <t>301899003</t>
+  </si>
+  <si>
+    <t>Dissection of proximal aorta [disorder]</t>
+  </si>
+  <si>
+    <t>233997009</t>
+  </si>
+  <si>
+    <t>Dissection of distal aorta [disorder]</t>
+  </si>
+  <si>
+    <t>27631000146108</t>
+  </si>
+  <si>
+    <t>Dissection of aortic arch [disorder]</t>
+  </si>
+  <si>
+    <t>45894003</t>
+  </si>
+  <si>
+    <t>Medionecrosis of aorta [disorder]</t>
+  </si>
+  <si>
+    <t>1303726005</t>
+  </si>
+  <si>
+    <t>Dissection of infrarenal aorta [disorder]</t>
+  </si>
+  <si>
+    <t>127013003</t>
+  </si>
+  <si>
+    <t>Disorder of kidney due to diabetes mellitus [disorder]</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Diabetes mellitus complicated by chronic kidney disease</t>
+  </si>
+  <si>
+    <t>408512008</t>
+  </si>
+  <si>
+    <t>Body mass index 40+ - severely obese [finding]</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Severe obesity</t>
+  </si>
+  <si>
+    <t>414027002</t>
+  </si>
+  <si>
+    <t>Disorder of hematopoietic structure [disorder]</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Chronic hematologic disorders</t>
+  </si>
+  <si>
+    <t>417357006</t>
+  </si>
+  <si>
+    <t>Sickling disorder due to hemoglobin S [disorder]</t>
+  </si>
+  <si>
+    <t>350586651000119105</t>
+  </si>
+  <si>
+    <t>Chronic respiratory failure due to neuromuscular disease [disorder]</t>
+  </si>
+  <si>
+    <t>260</t>
+  </si>
+  <si>
+    <t>Neurologic or neuromuscular conditions causing impaired airway clearance or respiratory muscle weakness</t>
+  </si>
+  <si>
+    <t>67750007</t>
+  </si>
+  <si>
+    <t>Ineffective airway clearance [finding]</t>
+  </si>
+  <si>
+    <t>160734000</t>
+  </si>
+  <si>
+    <t>Lives in nursing home [finding]</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>Resident of a nursing home</t>
+  </si>
+  <si>
+    <t>248279007</t>
+  </si>
+  <si>
+    <t>Frailty [finding]</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Frailty</t>
+  </si>
+  <si>
+    <t>230572002</t>
+  </si>
+  <si>
+    <t>Neuropathy due to diabetes mellitus [disorder]</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>Diabetes mellitus complicated by neuropathy</t>
+  </si>
+  <si>
+    <t>4855003</t>
+  </si>
+  <si>
+    <t>Retinopathy due to diabetes mellitus [disorder]</t>
+  </si>
+  <si>
+    <t>264</t>
+  </si>
+  <si>
+    <t>Diabetes mellitus complicated by retinopathy</t>
+  </si>
+  <si>
+    <t>170747006</t>
+  </si>
+  <si>
+    <t>Diabetic on insulin [finding]</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Diabetes requiring treatment with insulin</t>
+  </si>
+  <si>
+    <t>128531006</t>
+  </si>
+  <si>
+    <t>Islet cell transplant [procedure]</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Islet Transplantation</t>
+  </si>
+  <si>
+    <t>77465005</t>
+  </si>
+  <si>
+    <t>Transplantation [procedure]</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Transplantation</t>
+  </si>
+  <si>
+    <t>124950009</t>
+  </si>
+  <si>
+    <t>Deficiency of immunoglobulin [disorder]</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Immunoglobulin deficiency</t>
+  </si>
+  <si>
+    <t>80141007</t>
+  </si>
+  <si>
+    <t>hemoglobinopathy [disorder]</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Hemoglobinopathy disorder</t>
+  </si>
+  <si>
+    <t>67569000</t>
+  </si>
+  <si>
+    <t>Bronchopulmonary dysplasia of newborn [disorder]</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Chronic lung disease of prematurity</t>
   </si>
 </sst>
 </file>
@@ -422,74 +2603,76 @@
       <c r="A7" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -499,228 +2682,4189 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E246"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>29</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="C5" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s" s="2">
+      <c r="E5" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B9" t="s" s="2">
-        <v>56</v>
-      </c>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="B14" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
+      <c r="C14" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="E13" t="s" s="2">
-        <v>71</v>
+      <c r="B15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D61" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D62" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D64" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D65" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D66" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D67" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D68" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D70" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D72" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D73" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D74" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D75" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D76" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D79" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="E79" t="s" s="2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D80" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="E80" t="s" s="2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="E81" t="s" s="2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D82" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D84" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="E84" t="s" s="2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D85" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="E85" t="s" s="2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D86" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="E86" t="s" s="2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D87" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="E87" t="s" s="2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D88" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E88" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D89" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E89" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D90" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E90" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D91" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E91" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E92" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D93" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E93" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E94" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E95" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E97" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E98" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E99" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D100" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E100" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D101" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E101" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="E104" t="s" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="E105" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="E106" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="E107" t="s" s="2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D108" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="E108" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D109" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="E109" t="s" s="2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="E110" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="E111" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="E112" t="s" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="E113" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D114" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E114" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="E115" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="E116" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="E117" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="E118" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="E119" t="s" s="2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="E120" t="s" s="2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D121" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="E121" t="s" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D122" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="E122" t="s" s="2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D123" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="E123" t="s" s="2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D124" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="E124" t="s" s="2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D125" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="E125" t="s" s="2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D126" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="E126" t="s" s="2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D127" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="E127" t="s" s="2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D128" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="E128" t="s" s="2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D129" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="E129" t="s" s="2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D130" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="E130" t="s" s="2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D131" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="E131" t="s" s="2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D132" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="E132" t="s" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D133" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="E133" t="s" s="2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="E134" t="s" s="2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D135" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="E135" t="s" s="2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D136" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="E136" t="s" s="2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D137" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="E137" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D138" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="E138" t="s" s="2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D139" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="E139" t="s" s="2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D140" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="E140" t="s" s="2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D141" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="E141" t="s" s="2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D142" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="E142" t="s" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D143" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="E143" t="s" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D144" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="E144" t="s" s="2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D145" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="E145" t="s" s="2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D146" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="E146" t="s" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D147" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="E147" t="s" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C148" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D148" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="E148" t="s" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C149" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D149" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="E149" t="s" s="2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D150" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="E150" t="s" s="2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C151" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D151" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="E151" t="s" s="2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D152" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="E152" t="s" s="2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C153" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D153" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="E153" t="s" s="2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D154" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="E154" t="s" s="2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C155" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D155" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="E155" t="s" s="2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D156" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="E156" t="s" s="2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C157" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D157" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="E157" t="s" s="2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D158" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="E158" t="s" s="2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C159" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D159" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="E159" t="s" s="2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D160" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="E160" t="s" s="2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D161" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="E161" t="s" s="2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C162" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D162" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="E162" t="s" s="2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C163" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D163" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="E163" t="s" s="2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D164" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="E164" t="s" s="2">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D165" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="E165" t="s" s="2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D166" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="E166" t="s" s="2">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D167" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="E167" t="s" s="2">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C168" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D168" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="E168" t="s" s="2">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C169" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D169" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="E169" t="s" s="2">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C170" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D170" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="E170" t="s" s="2">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C171" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D171" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="E171" t="s" s="2">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C172" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D172" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="E172" t="s" s="2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C173" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D173" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E173" t="s" s="2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D174" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E174" t="s" s="2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C175" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D175" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="E175" t="s" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C176" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D176" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="E176" t="s" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D177" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="E177" t="s" s="2">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C178" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D178" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="E178" t="s" s="2">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D179" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="E179" t="s" s="2">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C180" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D180" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="E180" t="s" s="2">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D181" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="E181" t="s" s="2">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C182" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D182" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="E182" t="s" s="2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D183" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="E183" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D184" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="E184" t="s" s="2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C185" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D185" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="E185" t="s" s="2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D186" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="E186" t="s" s="2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D187" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="E187" t="s" s="2">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C188" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D188" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="E188" t="s" s="2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C189" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D189" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="E189" t="s" s="2">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D190" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="E190" t="s" s="2">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D191" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="E191" t="s" s="2">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D192" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="E192" t="s" s="2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C193" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D193" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="E193" t="s" s="2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C194" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D194" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="E194" t="s" s="2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D195" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="E195" t="s" s="2">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D196" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="E196" t="s" s="2">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C197" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D197" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="E197" t="s" s="2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D198" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="E198" t="s" s="2">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D199" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="E199" t="s" s="2">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D200" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="E200" t="s" s="2">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D201" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="E201" t="s" s="2">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C202" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D202" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="E202" t="s" s="2">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C203" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D203" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="E203" t="s" s="2">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C204" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D204" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="E204" t="s" s="2">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D205" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="E205" t="s" s="2">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C206" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D206" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="E206" t="s" s="2">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C207" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D207" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="E207" t="s" s="2">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C208" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D208" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="E208" t="s" s="2">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="C209" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D209" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="E209" t="s" s="2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D210" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="E210" t="s" s="2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C211" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D211" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="E211" t="s" s="2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C212" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D212" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="E212" t="s" s="2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C213" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D213" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="E213" t="s" s="2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C214" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D214" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="E214" t="s" s="2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C215" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D215" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="E215" t="s" s="2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="C216" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D216" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E216" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="C217" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D217" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E217" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="C218" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D218" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E218" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C219" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D219" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E219" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C220" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D220" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E220" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="C221" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D221" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E221" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C222" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D222" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E222" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="C223" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D223" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E223" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C224" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D224" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E224" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="C225" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D225" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E225" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C226" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D226" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E226" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C227" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D227" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E227" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C228" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D228" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E228" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C229" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D229" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E229" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C230" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D230" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="E230" t="s" s="2">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="C231" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D231" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="E231" t="s" s="2">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="C232" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D232" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="E232" t="s" s="2">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C233" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D233" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="E233" t="s" s="2">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="C234" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D234" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="E234" t="s" s="2">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C235" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D235" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="E235" t="s" s="2">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C236" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D236" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="E236" t="s" s="2">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="C237" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D237" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="E237" t="s" s="2">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="C238" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D238" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="E238" t="s" s="2">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C239" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D239" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="E239" t="s" s="2">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="C240" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D240" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="E240" t="s" s="2">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="C241" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D241" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="E241" t="s" s="2">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C242" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D242" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="E242" t="s" s="2">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="C243" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D243" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="E243" t="s" s="2">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="C244" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D244" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="E244" t="s" s="2">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="C245" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D245" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="E245" t="s" s="2">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="C246" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D246" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="E246" t="s" s="2">
+        <v>799</v>
       </c>
     </row>
   </sheetData>

--- a/cicada_ig/SnomedToCdsiObservation.xlsx
+++ b/cicada_ig/SnomedToCdsiObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:44:07-04:00</t>
+    <t>2026-09-06T23:13:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cicada_ig/SnomedToCdsiObservation.xlsx
+++ b/cicada_ig/SnomedToCdsiObservation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T23:13:14-04:00</t>
+    <t>2026-09-07T18:40:23-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cicada_ig/SnomedToCdsiObservation.xlsx
+++ b/cicada_ig/SnomedToCdsiObservation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="801">
   <si>
     <t>Property</t>
   </si>
@@ -36,6 +36,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>SnomedToCdsiObservation</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:40:23-04:00</t>
+    <t>2026-09-07T19:28:06-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2581,98 +2584,100 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2687,4184 +2692,4184 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>30</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E18" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E27" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>105</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E41" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E43" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D43" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="E43" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="E45" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>163</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D49" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>177</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="E58" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D58" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="E58" t="s" s="2">
-        <v>199</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D60" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="E60" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D60" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="E60" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="E63" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D63" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="E63" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D66" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="E66" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="E66" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="E69" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D69" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="E69" t="s" s="2">
-        <v>229</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="E71" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D71" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="E71" t="s" s="2">
-        <v>235</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="E77" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D77" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="E77" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D79" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="E79" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D79" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="E79" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="E83" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="E83" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D89" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="E89" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D89" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="E89" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="E97" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D97" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="E106" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D106" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="E106" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="E111" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D111" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="E111" t="s" s="2">
-        <v>349</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="E116" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D116" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="E116" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D134" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="E134" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D134" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="E134" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D135" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D137" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D139" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E139" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E140" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D141" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="E141" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D141" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="E141" t="s" s="2">
-        <v>461</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D143" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="E143" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D143" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="E143" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D145" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="E145" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D145" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="E145" t="s" s="2">
-        <v>473</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D146" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E146" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D147" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="E147" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="C147" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D147" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="E147" t="s" s="2">
-        <v>479</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D148" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E148" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D149" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D150" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="E150" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C150" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D150" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="E150" t="s" s="2">
-        <v>487</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D151" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C152" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D152" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="E152" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D152" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="E152" t="s" s="2">
-        <v>493</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D153" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D154" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="E154" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D154" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="E154" t="s" s="2">
-        <v>499</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D155" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D156" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D157" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D158" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="E158" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="C158" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D158" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="E158" t="s" s="2">
-        <v>513</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D159" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D160" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E160" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D161" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="E161" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D161" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="E161" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D162" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D163" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D164" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D165" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D166" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D167" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="E167" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C167" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D167" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="E167" t="s" s="2">
-        <v>543</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D168" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E168" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C169" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D169" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="E169" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D169" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="E169" t="s" s="2">
-        <v>549</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D170" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C171" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D171" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="E171" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C171" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D171" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="E171" t="s" s="2">
-        <v>555</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D172" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E172" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D173" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E173" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D174" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="E174" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C174" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D174" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="E174" t="s" s="2">
-        <v>565</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E175" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C176" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D176" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="E176" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D176" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="E176" t="s" s="2">
-        <v>571</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E177" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E178" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D179" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E179" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C180" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D180" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="E180" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D180" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="E180" t="s" s="2">
-        <v>583</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D181" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E181" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D182" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D183" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D184" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D185" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E185" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D186" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D187" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D188" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E188" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D189" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E189" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D190" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="E190" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D190" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="E190" t="s" s="2">
-        <v>621</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D191" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E191" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D192" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E192" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D193" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E193" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D194" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E194" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D195" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E195" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D196" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E196" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D197" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E197" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D198" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E198" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D199" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E199" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E200" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D201" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E201" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D202" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E202" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D203" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E203" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D204" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E204" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D205" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="E205" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="C205" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D205" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="E205" t="s" s="2">
-        <v>677</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D206" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E206" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D207" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E207" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D208" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E208" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D209" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E209" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D210" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E210" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C211" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D211" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="E211" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="B211" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C211" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D211" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="E211" t="s" s="2">
-        <v>697</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D212" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E212" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D213" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E213" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D214" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E214" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D215" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E215" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D216" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E216" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="C217" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D217" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="E217" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="B217" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="C217" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D217" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="E217" t="s" s="2">
-        <v>711</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D218" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E218" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D219" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E219" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D220" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E220" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D221" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E221" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D222" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E222" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D223" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E223" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D224" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E224" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D225" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E225" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D226" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E226" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D227" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E227" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D228" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E228" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D229" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E229" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D230" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E230" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D231" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E231" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D232" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E232" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D233" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E233" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="C234" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D234" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="E234" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="C234" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D234" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="E234" t="s" s="2">
-        <v>751</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D235" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E235" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="C236" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D236" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="E236" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="C236" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D236" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="E236" t="s" s="2">
-        <v>757</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D237" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E237" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D238" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E238" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D239" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E239" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D240" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="E240" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D241" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E241" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D242" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E242" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D243" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E243" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D244" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E244" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D245" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E245" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D246" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="E246" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/cicada_ig/SnomedToCdsiObservation.xlsx
+++ b/cicada_ig/SnomedToCdsiObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T19:28:06-04:00</t>
+    <t>2026-09-07T19:51:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
